--- a/artfynd/A 50916-2022 artfynd.xlsx
+++ b/artfynd/A 50916-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50916-2022 artfynd.xlsx
+++ b/artfynd/A 50916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66544429</v>
+        <v>112038148</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kraddsele V, Ly lm</t>
+          <t>Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562220.9010922704</v>
+        <v>562332</v>
       </c>
       <c r="R2" t="n">
-        <v>7307916.772885768</v>
+        <v>7307762</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,23 +757,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>25161</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +779,7 @@
         <v>66544381</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562301.1643018849</v>
+        <v>562301</v>
       </c>
       <c r="R3" t="n">
-        <v>7307748.702907878</v>
+        <v>7307749</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +844,9 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66544430</v>
+        <v>112038104</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +889,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kraddsele V, Ly lm</t>
+          <t>Djupfors, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562298.8568470892</v>
+        <v>562292</v>
       </c>
       <c r="R4" t="n">
-        <v>7307929.926454239</v>
+        <v>7307715</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,38 +960,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>25162</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112038127</v>
+        <v>112038151</v>
       </c>
       <c r="B5" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562313</v>
+        <v>562332</v>
       </c>
       <c r="R5" t="n">
-        <v>7307732</v>
+        <v>7307762</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,47 +1080,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112038209</v>
+        <v>112038127</v>
       </c>
       <c r="B6" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562326</v>
+        <v>562313</v>
       </c>
       <c r="R6" t="n">
-        <v>7307825</v>
+        <v>7307732</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,17 +1156,13 @@
           <t>2023-09-03</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1247,37 +1181,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112038151</v>
+        <v>112038197</v>
       </c>
       <c r="B7" t="n">
-        <v>89554</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,7 +1222,7 @@
         <v>562332</v>
       </c>
       <c r="R7" t="n">
-        <v>7307761</v>
+        <v>7307762</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112038148</v>
+        <v>112038209</v>
       </c>
       <c r="B8" t="n">
-        <v>89835</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,26 +1293,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562332</v>
+        <v>562326</v>
       </c>
       <c r="R8" t="n">
-        <v>7307761</v>
+        <v>7307825</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,13 +1363,17 @@
           <t>2023-09-03</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1456,536 +1389,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112038104</v>
-      </c>
-      <c r="B9" t="n">
-        <v>89550</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Djupfors, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>562292</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7307715</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112038197</v>
-      </c>
-      <c r="B10" t="n">
-        <v>77651</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Djupfors, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>562332</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7307761</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112038107</v>
-      </c>
-      <c r="B11" t="n">
-        <v>89572</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Djupfors, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>562292</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7307715</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112038198</v>
-      </c>
-      <c r="B12" t="n">
-        <v>89572</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Djupfors, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>562332</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7307761</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112038121</v>
-      </c>
-      <c r="B13" t="n">
-        <v>89572</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Djupfors, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>562313</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7307732</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-09-03</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50916-2022 artfynd.xlsx
+++ b/artfynd/A 50916-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038148</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544381</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038104</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038151</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038127</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038197</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,8 +1424,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112038209</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>